--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488111_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488111_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. HUNT</t>
+          <t>A. BUALÓ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3371</v>
+        <v>2.1133</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1279</v>
+        <v>2.1133</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7907999999999999</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>4.381</v>
+        <v>2.1133</v>
       </c>
       <c r="H2" t="n">
-        <v>2.003</v>
+        <v>0.908</v>
       </c>
       <c r="I2" t="n">
-        <v>2.378</v>
+        <v>1.2053</v>
       </c>
       <c r="J2" t="n">
-        <v>5.7435</v>
+        <v>2.1133</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1281</v>
+        <v>0.908</v>
       </c>
       <c r="L2" t="n">
-        <v>2.6154</v>
+        <v>1.2053</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3625</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1251</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2374</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1632</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2369</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4001</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BUALÓ</t>
+          <t>B. HUNT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1133</v>
+        <v>1.9783</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1133</v>
+        <v>3.1903</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-1.212</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1133</v>
+        <v>4.381</v>
       </c>
       <c r="H3" t="n">
-        <v>0.908</v>
+        <v>2.003</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2053</v>
+        <v>2.378</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1133</v>
+        <v>5.7435</v>
       </c>
       <c r="K3" t="n">
-        <v>0.908</v>
+        <v>3.1281</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2053</v>
+        <v>2.6154</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-1.3625</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-1.1251</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.2374</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.1956</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-1.1745</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.979</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.757</v>
+        <v>1.837</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0772</v>
+        <v>0.2415</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6797</v>
+        <v>1.5955</v>
       </c>
       <c r="G4" t="n">
         <v>0.3101</v>
@@ -766,13 +766,13 @@
         <v>2.5769</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4233</v>
+        <v>-0.3433</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4865</v>
+        <v>-1.3222</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0632</v>
+        <v>0.979</v>
       </c>
       <c r="V4" t="n">
         <v>1.4737</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2537</v>
+        <v>1.3836</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5027</v>
+        <v>1.6046</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.249</v>
+        <v>-0.2209</v>
       </c>
       <c r="G5" t="n">
         <v>0.9523</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3014</v>
+        <v>0.4314</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5543</v>
+        <v>0.6562</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2529</v>
+        <v>-0.2249</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.994</v>
+        <v>0.7975</v>
       </c>
       <c r="E6" t="n">
         <v>-0.1046</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0986</v>
+        <v>0.9021</v>
       </c>
       <c r="G6" t="n">
         <v>0.5635</v>
@@ -922,13 +922,13 @@
         <v>0.1982</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2323</v>
+        <v>0.0358</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3571</v>
+        <v>0.1606</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MARCOS GONZALEZ</t>
+          <t>F. MARIN FERRES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,31 +955,31 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3283</v>
+        <v>-0.6161</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0793</v>
+        <v>-0.3951</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.249</v>
+        <v>-0.2209</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6349</v>
+        <v>-1.314</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0915</v>
+        <v>-1.4498</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5433</v>
+        <v>0.1358</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6388</v>
+        <v>-1.3179</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0404</v>
+        <v>-1.3179</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6791</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0.0039</v>
@@ -1000,19 +1000,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9805</v>
+        <v>0.4314</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2335</v>
+        <v>0.6562</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2529</v>
+        <v>-0.2249</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.674</v>
+        <v>0.2666</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.674</v>
+        <v>0.2666</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. MARIN FERRES</t>
+          <t>A. MARCOS GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,31 +1033,31 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.746</v>
+        <v>-0.7077</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.497</v>
+        <v>-0.4867</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.249</v>
+        <v>-0.2209</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.314</v>
+        <v>-0.6349</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4498</v>
+        <v>-0.0915</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1358</v>
+        <v>-0.5433</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3179</v>
+        <v>-0.6388</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3179</v>
+        <v>0.0404</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.6791</v>
       </c>
       <c r="M8" t="n">
         <v>0.0039</v>
@@ -1078,19 +1078,19 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3014</v>
+        <v>0.6011</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5543</v>
+        <v>0.826</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2529</v>
+        <v>-0.2249</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2666</v>
+        <v>-0.674</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2666</v>
+        <v>-0.674</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8421</v>
+        <v>-1.5593</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8841</v>
+        <v>2.1108</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.7262</v>
+        <v>-3.6701</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2136</v>
@@ -1156,13 +1156,13 @@
         <v>1.784</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8179</v>
+        <v>-0.535</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1745</v>
+        <v>-0.9479</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3567</v>
+        <v>0.4128</v>
       </c>
       <c r="V9" t="n">
         <v>0.6036</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0132</v>
+        <v>-3.3602</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.468</v>
+        <v>-1.0958</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5452</v>
+        <v>-2.2644</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5447</v>
@@ -1234,13 +1234,13 @@
         <v>1.9822</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5581</v>
+        <v>0.2112</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2279</v>
+        <v>-0.3999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3303</v>
+        <v>0.611</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8107</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3578</v>
+        <v>-3.7789</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7099</v>
+        <v>-1.9344</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6479</v>
+        <v>-1.8444</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1401</v>
@@ -1312,13 +1312,13 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8212</v>
+        <v>-0.2423</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4351</v>
+        <v>-0.6597</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6139</v>
+        <v>0.4174</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6036</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3861</v>
+        <v>-4.3175</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6719</v>
+        <v>-2.5471</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7142</v>
+        <v>-1.7704</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1841</v>
@@ -1390,13 +1390,13 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1843</v>
+        <v>-0.1157</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6753</v>
+        <v>-0.5505</v>
       </c>
       <c r="U12" t="n">
-        <v>0.491</v>
+        <v>0.4349</v>
       </c>
       <c r="V12" t="n">
         <v>-3.0178</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.9119</v>
+        <v>-5.5667</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6496</v>
+        <v>-4.3605</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2623</v>
+        <v>-1.2062</v>
       </c>
       <c r="G13" t="n">
         <v>-1.1772</v>
@@ -1468,13 +1468,13 @@
         <v>1.9822</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4838</v>
+        <v>-0.1386</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5599</v>
+        <v>-1.2709</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0761</v>
+        <v>1.1323</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2775</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.3968</v>
+        <v>-6.7947</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.2296</v>
+        <v>-4.1048</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.1672</v>
+        <v>-2.6899</v>
       </c>
       <c r="G14" t="n">
         <v>-1.8067</v>
@@ -1546,13 +1546,13 @@
         <v>1.3876</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7336</v>
+        <v>-1.1315</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2993</v>
+        <v>-1.1745</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4343</v>
+        <v>0.043</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0813</v>
@@ -1579,19 +1579,19 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-19.5271</v>
+        <v>-18.5914</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.7047</v>
+        <v>-5.7685</v>
       </c>
       <c r="F15" t="n">
         <v>-12.8225</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.695099999999999</v>
+        <v>-6.6951</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.356400000000001</v>
+        <v>-3.3564</v>
       </c>
       <c r="I15" t="n">
         <v>-3.3386</v>
@@ -1624,13 +1624,13 @@
         <v>13.8755</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9272</v>
+        <v>-0.9911000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-6.4223</v>
+        <v>-5.486499999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>4.4954</v>
+        <v>4.495299999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-7.931699999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>9.518800000000001</v>
+        <v>10.0562</v>
       </c>
       <c r="E16" t="n">
-        <v>4.665</v>
+        <v>5.1743</v>
       </c>
       <c r="F16" t="n">
-        <v>4.8538</v>
+        <v>4.8819</v>
       </c>
       <c r="G16" t="n">
         <v>4.9818</v>
@@ -1702,13 +1702,13 @@
         <v>2.7751</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2683</v>
+        <v>0.8057</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4975</v>
+        <v>-0.9882</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7658</v>
+        <v>1.7939</v>
       </c>
       <c r="V16" t="n">
         <v>2.4846</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>9.2723</v>
+        <v>6.883</v>
       </c>
       <c r="E17" t="n">
-        <v>8.709099999999999</v>
+        <v>6.7736</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5632</v>
+        <v>0.1094</v>
       </c>
       <c r="G17" t="n">
         <v>2.1076</v>
@@ -1780,13 +1780,13 @@
         <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4135</v>
+        <v>1.0241</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3973</v>
+        <v>0.4618</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0162</v>
+        <v>0.5624</v>
       </c>
       <c r="V17" t="n">
         <v>3.3547</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7111</v>
+        <v>4.9636</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0709</v>
+        <v>3.6821</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6402</v>
+        <v>1.2815</v>
       </c>
       <c r="G18" t="n">
         <v>2.6412</v>
@@ -1858,13 +1858,13 @@
         <v>2.5769</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8707</v>
+        <v>0.3818</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3727</v>
+        <v>-0.7615</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5021</v>
+        <v>1.1433</v>
       </c>
       <c r="V18" t="n">
         <v>1.5441</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.1566</v>
+        <v>3.9422</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0929</v>
+        <v>2.6022</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0637</v>
+        <v>1.3399</v>
       </c>
       <c r="G19" t="n">
         <v>3.8559</v>
@@ -1936,13 +1936,13 @@
         <v>2.5769</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1046</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4975</v>
+        <v>-0.9882</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3929</v>
+        <v>1.6691</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.1439</v>
+        <v>3.4599</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3368</v>
+        <v>2.5405</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8071</v>
+        <v>0.9194</v>
       </c>
       <c r="G20" t="n">
         <v>0.0066</v>
@@ -2014,13 +2014,13 @@
         <v>1.3876</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0609</v>
+        <v>0.2551</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1232</v>
+        <v>-0.9194</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0622</v>
+        <v>1.1745</v>
       </c>
       <c r="V20" t="n">
         <v>1.8107</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. CALDERON QUINONES</t>
+          <t>R. HIDALGO SALAZAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1551</v>
+        <v>0.2213</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6571</v>
+        <v>0.1817</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5019</v>
+        <v>0.0396</v>
       </c>
       <c r="G21" t="n">
         <v>0.3159</v>
@@ -2092,28 +2092,28 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1608</v>
+        <v>-0.502</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6167</v>
+        <v>0.1413</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7775</v>
+        <v>-0.6434</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.4074</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. HIDALGO SALAZAR</t>
+          <t>R. CALDERON QUINONES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1018</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.022</v>
+        <v>0.3515</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1238</v>
+        <v>-0.4458</v>
       </c>
       <c r="G22" t="n">
         <v>0.3159</v>
@@ -2170,28 +2170,28 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.4102</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0624</v>
+        <v>0.3111</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5591</v>
+        <v>-0.7214</v>
       </c>
       <c r="V22" t="n">
-        <v>0.4074</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.4074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CALDERON QUINONES</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6987</v>
+        <v>-0.3326</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0422</v>
+        <v>3.0008</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6565</v>
+        <v>-3.3335</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1599</v>
+        <v>-0.1166</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0241</v>
+        <v>0.0575</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1358</v>
+        <v>-0.1742</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0202</v>
+        <v>2.2708</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0202</v>
+        <v>0.1816</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.0892</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1398</v>
+        <v>-2.3875</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0039</v>
+        <v>-0.1241</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1358</v>
+        <v>-2.2634</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8586</v>
+        <v>0.3964</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0624</v>
+        <v>-0.2789</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7962</v>
+        <v>0.6753</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>J. CALDERON QUINONES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.9883</v>
+        <v>-0.4669</v>
       </c>
       <c r="E24" t="n">
-        <v>2.5934</v>
+        <v>0.1615</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5816</v>
+        <v>-0.6284</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1166</v>
+        <v>0.1599</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0575</v>
+        <v>0.0241</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1742</v>
+        <v>0.1358</v>
       </c>
       <c r="J24" t="n">
-        <v>2.2708</v>
+        <v>0.0202</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1816</v>
+        <v>0.0202</v>
       </c>
       <c r="L24" t="n">
-        <v>2.0892</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.3875</v>
+        <v>0.1398</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1241</v>
+        <v>0.0039</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.2634</v>
+        <v>0.1358</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2592</v>
+        <v>-0.6268</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6864</v>
+        <v>0.1413</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4272</v>
+        <v>-0.7682</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>A. MONTENEGRO MOYA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.4889</v>
+        <v>-1.445</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.4284</v>
+        <v>-1.3685</v>
       </c>
       <c r="F25" t="n">
-        <v>2.9395</v>
+        <v>-0.0765</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.0441</v>
+        <v>-1.4915</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.442</v>
+        <v>-0.9941</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3979</v>
+        <v>-0.4974</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0641</v>
+        <v>-1.2374</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.309</v>
+        <v>-0.5984</v>
       </c>
       <c r="L25" t="n">
-        <v>0.245</v>
+        <v>-0.639</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.98</v>
+        <v>-0.2542</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1329</v>
+        <v>-0.3957</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1529</v>
+        <v>0.1415</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.3698</v>
+        <v>0.5947</v>
       </c>
       <c r="Q25" t="n">
-        <v>-5.1538</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.784</v>
+        <v>0.5947</v>
       </c>
       <c r="S25" t="n">
-        <v>2.251</v>
+        <v>-0.6185</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7894</v>
+        <v>-0.1312</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4615</v>
+        <v>-0.4874</v>
       </c>
       <c r="V25" t="n">
-        <v>0.674</v>
+        <v>0.0704</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.674</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. MONTENEGRO MOYA</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.9472</v>
+        <v>-2.6983</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6742</v>
+        <v>-5.549</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.273</v>
+        <v>2.8507</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.4915</v>
+        <v>-1.0441</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.9941</v>
+        <v>-1.442</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4974</v>
+        <v>0.3979</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.2374</v>
+        <v>-0.0641</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5984</v>
+        <v>-0.309</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.639</v>
+        <v>0.245</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2542</v>
+        <v>-0.98</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.3957</v>
+        <v>-1.1329</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1415</v>
+        <v>0.1529</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5947</v>
+        <v>-3.3698</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-5.1538</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5947</v>
+        <v>1.784</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1207</v>
+        <v>1.0416</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4368</v>
+        <v>-0.3311</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6839</v>
+        <v>1.3727</v>
       </c>
       <c r="V26" t="n">
-        <v>0.0704</v>
+        <v>0.674</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0704</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.4094</v>
+        <v>-4.2827</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.1357</v>
+        <v>-4.7282</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.4455</v>
       </c>
       <c r="G27" t="n">
         <v>-5.0377</v>
@@ -2560,13 +2560,13 @@
         <v>2.7751</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0514</v>
+        <v>0.1781</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.5599</v>
+        <v>-1.1525</v>
       </c>
       <c r="U27" t="n">
-        <v>1.6113</v>
+        <v>1.3305</v>
       </c>
       <c r="V27" t="n">
         <v>-1.2071</v>
@@ -2593,37 +2593,37 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>19.5271</v>
+        <v>20.2064</v>
       </c>
       <c r="E28" t="n">
-        <v>12.8227</v>
+        <v>12.8225</v>
       </c>
       <c r="F28" t="n">
-        <v>6.7046</v>
+        <v>7.3837</v>
       </c>
       <c r="G28" t="n">
-        <v>6.694899999999998</v>
+        <v>6.6949</v>
       </c>
       <c r="H28" t="n">
         <v>3.356300000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>3.338700000000001</v>
+        <v>3.3387</v>
       </c>
       <c r="J28" t="n">
         <v>19.7965</v>
       </c>
       <c r="K28" t="n">
-        <v>9.951600000000001</v>
+        <v>9.951600000000003</v>
       </c>
       <c r="L28" t="n">
-        <v>9.844799999999999</v>
+        <v>9.844800000000001</v>
       </c>
       <c r="M28" t="n">
         <v>-13.1013</v>
       </c>
       <c r="N28" t="n">
-        <v>-6.595199999999999</v>
+        <v>-6.5952</v>
       </c>
       <c r="O28" t="n">
         <v>-6.506200000000001</v>
@@ -2638,13 +2638,13 @@
         <v>16.849</v>
       </c>
       <c r="S28" t="n">
-        <v>1.9272</v>
+        <v>2.6062</v>
       </c>
       <c r="T28" t="n">
-        <v>-4.4954</v>
+        <v>-4.4955</v>
       </c>
       <c r="U28" t="n">
-        <v>6.422499999999999</v>
+        <v>7.1013</v>
       </c>
       <c r="V28" t="n">
         <v>7.931699999999998</v>
